--- a/lab 14/data.xlsx
+++ b/lab 14/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\邱\Documents\Labsforclaude\lab 14\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\邱\Documents\Labsforothers\lab 14\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3EE01F4-41CE-47AD-9D27-333612E18A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3349DB6-78AD-405B-A9D7-AFC09EE77508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24" yWindow="0" windowWidth="11088" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11772" yWindow="0" windowWidth="11088" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -450,10 +450,10 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
         <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -475,11 +475,11 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="1">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="C2" s="6">
         <v>37</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.56000000000000005</v>
       </c>
       <c r="D2" s="1">
         <v>21.8</v>
@@ -492,11 +492,11 @@
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="1">
+        <v>1.06</v>
+      </c>
+      <c r="C3" s="6">
         <v>38</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1.06</v>
       </c>
       <c r="D3" s="1">
         <v>42</v>
@@ -509,11 +509,11 @@
       <c r="A4" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0.98</v>
       </c>
       <c r="D4" s="2">
         <v>42</v>
@@ -526,11 +526,11 @@
       <c r="A5" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="1">
+        <v>0.82</v>
+      </c>
+      <c r="C5" s="6">
         <v>39</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0.82</v>
       </c>
       <c r="D5" s="1">
         <v>31.9</v>
@@ -543,11 +543,11 @@
       <c r="A6" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="C6" s="6">
         <v>40</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0.18</v>
       </c>
       <c r="D6" s="1">
         <v>12</v>
@@ -560,7 +560,7 @@
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="3">
+      <c r="B7" s="3">
         <v>1.1200000000000001</v>
       </c>
       <c r="F7" s="3">
@@ -574,7 +574,7 @@
       <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="5">
+      <c r="B8" s="5">
         <v>1</v>
       </c>
       <c r="F8" s="3">
@@ -588,7 +588,7 @@
       <c r="A9" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="3">
+      <c r="B9" s="3">
         <v>0.86</v>
       </c>
       <c r="F9" s="3">
@@ -602,7 +602,7 @@
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="3">
+      <c r="B10" s="3">
         <v>0.72</v>
       </c>
       <c r="F10" s="3">
@@ -616,7 +616,7 @@
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="5">
+      <c r="B11" s="5">
         <v>0.57999999999999996</v>
       </c>
       <c r="F11" s="3">
@@ -630,7 +630,7 @@
       <c r="A12" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="5">
+      <c r="B12" s="5">
         <v>0.44</v>
       </c>
       <c r="F12" s="3">
@@ -640,11 +640,11 @@
         <v>3.6269999999999997E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="3">
+      <c r="B13" s="3">
         <v>0.28000000000000003</v>
       </c>
       <c r="F13" s="3">
@@ -658,7 +658,7 @@
       <c r="A14" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="3">
+      <c r="B14" s="3">
         <v>0.12</v>
       </c>
       <c r="F14" s="3">
@@ -672,7 +672,7 @@
       <c r="A15" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="3">
+      <c r="B15" s="3">
         <v>0</v>
       </c>
       <c r="F15" s="3">
@@ -686,7 +686,7 @@
       <c r="A16" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="1">
+      <c r="B16" s="1">
         <v>3.49E-2</v>
       </c>
       <c r="H16" s="1">
@@ -697,7 +697,7 @@
       <c r="A17" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="1">
+      <c r="B17" s="1">
         <v>4.7399999999999998E-2</v>
       </c>
       <c r="H17" s="4">
@@ -708,7 +708,7 @@
       <c r="A18" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="1">
+      <c r="B18" s="1">
         <v>5.2400000000000002E-2</v>
       </c>
       <c r="H18" s="4">
@@ -719,7 +719,7 @@
       <c r="A19" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="1">
+      <c r="B19" s="1">
         <v>6.4699999999999994E-2</v>
       </c>
       <c r="H19" s="4">
@@ -730,7 +730,7 @@
       <c r="A20" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="1">
+      <c r="B20" s="1">
         <v>7.5600000000000001E-2</v>
       </c>
       <c r="H20" s="1">
@@ -741,7 +741,7 @@
       <c r="A21" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="1">
+      <c r="B21" s="1">
         <v>7.7299999999999994E-2</v>
       </c>
       <c r="H21" s="1">
